--- a/separated_by_section/National_Transportation_System.xlsx
+++ b/separated_by_section/National_Transportation_System.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P225"/>
+  <dimension ref="A1:P363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,7 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
@@ -16071,6 +16071,9700 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>573384</v>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t>FAQ: Indexation of minimum liability insurance amounts</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/faq-indexation-minimum-liability-insurance-amounts</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faq-indexation-des-montants-minimums-dassurance-responsabilite-prescrits</t>
+        </is>
+      </c>
+      <c r="E226" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, January 20, 2026</t>
+        </is>
+      </c>
+      <c r="F226" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G226" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H226" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I226" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J226" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K226" s="1" t="inlineStr"/>
+      <c r="L226" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="M226" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="N226" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="O226" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P226" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>573383</v>
+      </c>
+      <c r="B227" s="1" t="inlineStr">
+        <is>
+          <t>Indexation of minimum liability insurance amounts – Effective July 1, 2026</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/indexation-minimum-liability-insurance-amounts-effective-july-1-2026</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/indexation-montants-minimums-assurance-responsabilite-prescrits-vigueur-1er-juillet-2026</t>
+        </is>
+      </c>
+      <c r="E227" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, January 20, 2026</t>
+        </is>
+      </c>
+      <c r="F227" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G227" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H227" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I227" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J227" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K227" s="1" t="inlineStr"/>
+      <c r="L227" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="M227" s="1" t="n">
+        <v>746</v>
+      </c>
+      <c r="N227" s="1" t="n">
+        <v>774</v>
+      </c>
+      <c r="O227" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P227" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>572983</v>
+      </c>
+      <c r="B228" s="1" t="inlineStr">
+        <is>
+          <t>CTA announces Volume-Related Composite Price Indices for Crop Year 2025–2026 for CN and CPKC</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/cta-announces-volume-related-composite-price-indices-crop-year-2025-2026-cn-and-cpkc</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/lotc-annonce-indices-des-prix-composites-afferents-au-volume-pour-campagne-agricole-2025</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, April 30, 2025</t>
+        </is>
+      </c>
+      <c r="F228" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G228" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H228" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I228" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J228" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K228" s="1" t="inlineStr"/>
+      <c r="L228" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="M228" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="N228" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="O228" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P228" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>570679</v>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t>The Canadian Transportation Agency issues final determination on whether Flair is Canadian</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/canadian-transportation-agency-issues-final-determination-whether-flair-canadian</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/loffice-des-transports-canada-emet-sa-determination-definitive-a-savoir-si-flair-est</t>
+        </is>
+      </c>
+      <c r="E229" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 1, 2022</t>
+        </is>
+      </c>
+      <c r="F229" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G229" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H229" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I229" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J229" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K229" s="1" t="inlineStr"/>
+      <c r="L229" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="M229" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="N229" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="O229" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P229" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>570531</v>
+      </c>
+      <c r="B230" s="1" t="inlineStr">
+        <is>
+          <t>The Canadian Transportation Agency issues preliminary determination on whether Flair is Canadian</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/canadian-transportation-agency-issues-preliminary-determination-whether-flair-canadian</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/loffice-des-transports-canada-a-emis-une-determination-preliminaire-sur-question-savoir-si</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, March 3, 2022</t>
+        </is>
+      </c>
+      <c r="F230" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G230" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I230" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J230" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K230" s="1" t="inlineStr"/>
+      <c r="L230" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="M230" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="N230" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="O230" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P230" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>573078</v>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>Consultation on request for exemptions from Filing and Publication Requirements for Tolls set out in air carriers' tariffs</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/consultation-request-exemptions-filing-and-publication-requirements-tolls-set-out</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/consultation/consultation-sur-demande-dexemptions-lapplication-des-obligations-deposer-et-publier</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 25, 2025</t>
+        </is>
+      </c>
+      <c r="F231" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G231" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H231" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I231" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J231" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K231" s="1" t="inlineStr"/>
+      <c r="L231" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="M231" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="N231" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="O231" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P231" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>570577</v>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t>Forward Regulatory Plan: 2022 to 2024 - Regulation on New Refund Requirements for Airlines</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/forward-regulatory-plan-2022-2024-regulation-new-refund-requirements-airlines</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/plan-prospectif-reglementation-pour-periode-2022-a-2024-reglement-sur-nouvelles-exigences</t>
+        </is>
+      </c>
+      <c r="E232" s="1" t="inlineStr">
+        <is>
+          <t>Friday, April 1, 2022</t>
+        </is>
+      </c>
+      <c r="F232" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G232" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H232" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I232" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J232" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K232" s="1" t="inlineStr"/>
+      <c r="L232" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M232" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N232" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O232" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P232" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>570061</v>
+      </c>
+      <c r="B233" s="1" t="inlineStr">
+        <is>
+          <t>The Canadian Transportation Agency (CTA) service standards and performance information for fiscal year 2019 to 2020</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/canadian-transportation-agency-cta-service-standards-and-performance-information-fiscal-year-2019</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/normes-service-et-rendement-loffice-des-transports-canada-exercice-2019-2020</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, July 21, 2020</t>
+        </is>
+      </c>
+      <c r="F233" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G233" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H233" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I233" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J233" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K233" s="1" t="inlineStr"/>
+      <c r="L233" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="M233" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="N233" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="O233" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P233" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>569021</v>
+      </c>
+      <c r="B234" s="1" t="inlineStr">
+        <is>
+          <t>Effective December 28th, 2019 - Notification to Air Carriers of Upward Revision of the Limits of Liability Governed by the Montreal Convention</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/effective-december-28th-2019-notification-air-carriers-upward-revision-limits-liability-governed</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/vigueur-28-decembre-2019-avis-aux-transporteurs-aeriens-concernant-revision-a-hausse-des-limites</t>
+        </is>
+      </c>
+      <c r="E234" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 24, 2019</t>
+        </is>
+      </c>
+      <c r="F234" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G234" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H234" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I234" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J234" s="1" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="K234" s="1" t="inlineStr">
+        <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
+      <c r="L234" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="M234" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="N234" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="O234" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P234" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>418804</v>
+      </c>
+      <c r="B235" s="1" t="inlineStr">
+        <is>
+          <t>Carriers that file tariffs with the Agency</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/carriers-who-file-tariffs-agency</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/transporteurs-qui-d%C3%A9posent-leurs-tarifs-aupr%C3%A8s-de-l%E2%80%99office</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, October 15, 2025</t>
+        </is>
+      </c>
+      <c r="F235" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G235" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H235" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I235" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J235" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K235" s="1" t="inlineStr"/>
+      <c r="L235" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="M235" s="1" t="n">
+        <v>387</v>
+      </c>
+      <c r="N235" s="1" t="n">
+        <v>436</v>
+      </c>
+      <c r="O235" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P235" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>418663</v>
+      </c>
+      <c r="B236" s="1" t="inlineStr">
+        <is>
+          <t>Fifth/Seventh Freedom Charter Flights Approved by the Agency</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/fifthseventh-freedom-charter-flights-approved-agency</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/vols-affretes-cinquieme-ou-septieme-liberte-approuves-par-loffice</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="inlineStr">
+        <is>
+          <t>Monday, November 2, 2015</t>
+        </is>
+      </c>
+      <c r="F236" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G236" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H236" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I236" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J236" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K236" s="1" t="inlineStr"/>
+      <c r="L236" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="M236" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="N236" s="1" t="n">
+        <v>307</v>
+      </c>
+      <c r="O236" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P236" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>93634</v>
+      </c>
+      <c r="B237" s="1" t="inlineStr">
+        <is>
+          <t>Agency-approved cost of capital rates for other regulatory purposes</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/agency-approved-cost-capital-rates-other</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/taux-du-capital-approuves-par-loffice-aux-fins-reglementaires-autres</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="inlineStr">
+        <is>
+          <t>Friday, December 5, 2025</t>
+        </is>
+      </c>
+      <c r="F237" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G237" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H237" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I237" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J237" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K237" s="1" t="inlineStr"/>
+      <c r="L237" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="M237" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="N237" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="O237" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P237" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>572828</v>
+      </c>
+      <c r="B238" s="1" t="inlineStr">
+        <is>
+          <t>Notification to air carriers of upward revision of the limits of liability governed by the Montreal Convention</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/notification-air-carriers-upward-revision-limits-liability-governed-montreal-convention</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/avis-aux-transporteurs-aeriens-concernant-revision-a-hausse-des-limites-responsabilite</t>
+        </is>
+      </c>
+      <c r="E238" s="1" t="inlineStr">
+        <is>
+          <t>Monday, December 23, 2024</t>
+        </is>
+      </c>
+      <c r="F238" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G238" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H238" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I238" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J238" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K238" s="1" t="inlineStr"/>
+      <c r="L238" s="1" t="n">
+        <v>1924</v>
+      </c>
+      <c r="M238" s="1" t="n">
+        <v>2449</v>
+      </c>
+      <c r="N238" s="1" t="n">
+        <v>2533</v>
+      </c>
+      <c r="O238" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P238" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>572407</v>
+      </c>
+      <c r="B239" s="1" t="inlineStr">
+        <is>
+          <t>Notice to Industry: Standard Point Location Codes</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/notice-industry-standard-point-location-codes</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/avis-a-lindustrie-code-unifie-des-localites-desservies</t>
+        </is>
+      </c>
+      <c r="E239" s="1" t="inlineStr">
+        <is>
+          <t>Monday, April 15, 2024</t>
+        </is>
+      </c>
+      <c r="F239" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G239" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H239" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I239" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J239" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K239" s="1" t="inlineStr"/>
+      <c r="L239" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="M239" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="N239" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="O239" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P239" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>97127</v>
+      </c>
+      <c r="B240" s="1" t="inlineStr">
+        <is>
+          <t>Fractional Ownership - Is a licence required from the Agency?</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/fractional-ownership-a-licence-required-agency</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/multipropriete-est-ce-quune-licence-loffice-est-necessaire</t>
+        </is>
+      </c>
+      <c r="E240" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, May 15, 2014</t>
+        </is>
+      </c>
+      <c r="F240" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G240" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H240" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I240" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J240" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K240" s="1" t="inlineStr"/>
+      <c r="L240" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="M240" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="N240" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="O240" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P240" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>418172</v>
+      </c>
+      <c r="B241" s="1" t="inlineStr">
+        <is>
+          <t>Limits of liability for passengers and goods</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/limits-liability-passengers-and-goods</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/limites-responsabilite-pour-passagers-et-marchandises</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="inlineStr">
+        <is>
+          <t>Friday, December 27, 2024</t>
+        </is>
+      </c>
+      <c r="F241" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G241" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H241" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I241" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J241" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K241" s="1" t="inlineStr"/>
+      <c r="L241" s="1" t="n">
+        <v>12144</v>
+      </c>
+      <c r="M241" s="1" t="n">
+        <v>15310</v>
+      </c>
+      <c r="N241" s="1" t="n">
+        <v>15298</v>
+      </c>
+      <c r="O241" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P241" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>571931</v>
+      </c>
+      <c r="B242" s="1" t="inlineStr">
+        <is>
+          <t>Guide to Railway Charges for Crossing Maintenance and Construction 2023</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/guide-railway-charges-crossing-maintenance-and-construction-2023</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/guide-des-frais-ferroviaires-pour-lentretien-et-construction-des-franchissements-2023</t>
+        </is>
+      </c>
+      <c r="E242" s="1" t="inlineStr">
+        <is>
+          <t>Friday, September 15, 2023</t>
+        </is>
+      </c>
+      <c r="F242" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G242" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H242" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I242" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J242" s="1" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="K242" s="1" t="inlineStr">
+        <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
+      <c r="L242" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="M242" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="N242" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="O242" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P242" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>571700</v>
+      </c>
+      <c r="B243" s="1" t="inlineStr">
+        <is>
+          <t>Notice to Industry: Updated Guidelines for Coasting Trade Licence Applications</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/notice-industry-updated-guidelines-coasting-trade-licence-applications</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/avis-a-lindustrie-mise-a-jour-des-lignes-directrices-relatives-aux-demandes-licences</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, June 29, 2023</t>
+        </is>
+      </c>
+      <c r="F243" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G243" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H243" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I243" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J243" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K243" s="1" t="inlineStr"/>
+      <c r="L243" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="M243" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="N243" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="O243" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P243" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>569769</v>
+      </c>
+      <c r="B244" s="1" t="inlineStr">
+        <is>
+          <t>International Air Charters: A Guide</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/international-air-charters-a-guide</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/guide-sur-services-daffretement-aerien-internationaux</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="inlineStr">
+        <is>
+          <t>Monday, December 14, 2020</t>
+        </is>
+      </c>
+      <c r="F244" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G244" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H244" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I244" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J244" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K244" s="1" t="inlineStr"/>
+      <c r="L244" s="1" t="n">
+        <v>484</v>
+      </c>
+      <c r="M244" s="1" t="n">
+        <v>759</v>
+      </c>
+      <c r="N244" s="1" t="n">
+        <v>735</v>
+      </c>
+      <c r="O244" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P244" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>97553</v>
+      </c>
+      <c r="B245" s="1" t="inlineStr">
+        <is>
+          <t>Apportionment of Costs of Grade Separations: A Resource Tool</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/apportionment-costs-grade-separations-a-resource-tool</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/repartition-des-couts-des-sauts-mouton-un-outil-dinformation</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="inlineStr">
+        <is>
+          <t>Monday, November 14, 2011</t>
+        </is>
+      </c>
+      <c r="F245" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G245" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H245" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I245" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J245" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K245" s="1" t="inlineStr"/>
+      <c r="L245" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="M245" s="1" t="n">
+        <v>441</v>
+      </c>
+      <c r="N245" s="1" t="n">
+        <v>507</v>
+      </c>
+      <c r="O245" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P245" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>97546</v>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t>Transfer and Discontinuance of Railway Line Operations and Railway Track Determinations: A Resource Tool</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/transfer-and-discontinuance-railway-line-operations-and-railway-track-determinations-resource-tool</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/transferts-et-cessation-lexploitation-lignes-chemin-fer-et-decisions-connexes-un-outil</t>
+        </is>
+      </c>
+      <c r="E246" s="1" t="inlineStr">
+        <is>
+          <t>Monday, November 14, 2011</t>
+        </is>
+      </c>
+      <c r="F246" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G246" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H246" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I246" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J246" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K246" s="1" t="inlineStr"/>
+      <c r="L246" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="M246" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="N246" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="O246" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P246" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>97672</v>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
+        <is>
+          <t>Guide to Certificates of Fitness</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/guide-certificates-fitness</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/guide-sur-certificats-daptitude</t>
+        </is>
+      </c>
+      <c r="E247" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, May 6, 2008</t>
+        </is>
+      </c>
+      <c r="F247" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G247" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H247" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I247" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J247" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K247" s="1" t="inlineStr"/>
+      <c r="L247" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="M247" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="N247" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="O247" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P247" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>566790</v>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
+        <is>
+          <t>Complaints about rail noise and vibration</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/complaints-about-rail-noise-and-vibration</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/plaintes-liees-au-bruit-et-aux-vibrations-ferroviaires</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="inlineStr">
+        <is>
+          <t>Monday, February 8, 2021</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G248" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H248" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I248" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J248" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K248" s="1" t="inlineStr"/>
+      <c r="L248" s="1" t="n">
+        <v>754</v>
+      </c>
+      <c r="M248" s="1" t="n">
+        <v>1037</v>
+      </c>
+      <c r="N248" s="1" t="n">
+        <v>963</v>
+      </c>
+      <c r="O248" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P248" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>93019</v>
+      </c>
+      <c r="B249" s="1" t="inlineStr">
+        <is>
+          <t>How to apply for a coasting trade licence</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/coasting-trade</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/lignes-directrices-de-loffice-sur-les-demandes-de-cabotage-1</t>
+        </is>
+      </c>
+      <c r="E249" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, June 29, 2023</t>
+        </is>
+      </c>
+      <c r="F249" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G249" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H249" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I249" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J249" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K249" s="1" t="inlineStr"/>
+      <c r="L249" s="1" t="n">
+        <v>335</v>
+      </c>
+      <c r="M249" s="1" t="n">
+        <v>433</v>
+      </c>
+      <c r="N249" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="O249" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P249" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>93792</v>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t>Agreements: railway crossings and construction</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/agreements-railway-crossings-and-construction</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ententes-sur-franchissements</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t>Friday, July 8, 2016</t>
+        </is>
+      </c>
+      <c r="F250" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G250" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H250" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I250" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J250" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K250" s="1" t="inlineStr"/>
+      <c r="L250" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="M250" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="N250" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="O250" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P250" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>571045</v>
+      </c>
+      <c r="B251" s="1" t="inlineStr">
+        <is>
+          <t>Railway Certificates of Fitness are now accessible</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/railway-certificates-fitness-are-now-accessible</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/certificats-daptitude-ferroviaires-sont-maintenant-accessibles-a-tous</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t>Monday, November 28, 2022</t>
+        </is>
+      </c>
+      <c r="F251" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G251" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H251" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I251" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J251" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K251" s="1" t="inlineStr"/>
+      <c r="L251" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="M251" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="N251" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="O251" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P251" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>97508</v>
+      </c>
+      <c r="B252" s="1" t="inlineStr">
+        <is>
+          <t>Railway Crossings of Other Railways: A Resource Tool</t>
+        </is>
+      </c>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/railway-crossings-other-railways-a-resource-tool</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/croisements-lignes-chemin-fer-un-outil-dinformation</t>
+        </is>
+      </c>
+      <c r="E252" s="1" t="inlineStr">
+        <is>
+          <t>Friday, April 22, 2016</t>
+        </is>
+      </c>
+      <c r="F252" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G252" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H252" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I252" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J252" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K252" s="1" t="inlineStr"/>
+      <c r="L252" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="M252" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="N252" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="O252" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P252" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>97522</v>
+      </c>
+      <c r="B253" s="1" t="inlineStr">
+        <is>
+          <t>Relocation of Railway Lines in Urban Areas: A Resource Tool</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/relocation-railway-lines-urban-areas-a-resource-tool</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/deplacement-des-lignes-chemin-fer-dans-des-zones-urbaines-un-outil-dinformation</t>
+        </is>
+      </c>
+      <c r="E253" s="1" t="inlineStr">
+        <is>
+          <t>Monday, November 14, 2011</t>
+        </is>
+      </c>
+      <c r="F253" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G253" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H253" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I253" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J253" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K253" s="1" t="inlineStr"/>
+      <c r="L253" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="M253" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="N253" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="O253" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P253" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>566809</v>
+      </c>
+      <c r="B254" s="1" t="inlineStr">
+        <is>
+          <t>Arbitration: Rail level of service</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/arbitration-rail-level-service</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/arbitrage-ferroviaire-portant-sur-niveau-service</t>
+        </is>
+      </c>
+      <c r="E254" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, June 21, 2016</t>
+        </is>
+      </c>
+      <c r="F254" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G254" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H254" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I254" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J254" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K254" s="1" t="inlineStr"/>
+      <c r="L254" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="M254" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="N254" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="O254" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P254" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>566235</v>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t>Memorandum of Understanding Between the Canadian Transportation Agency and the United States Surface Transportation Board Concerning Engagement and Information Sharing</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/memorandum-understanding-between-canadian-transportation-agency-and-united-states-surface</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/protocole-dentente-entre-loffice-des-transports-du-canada-et-le-united-states-surface-transportation-board-concernant-lengagement-et-le-partage-de-linformation</t>
+        </is>
+      </c>
+      <c r="E255" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 13, 2016</t>
+        </is>
+      </c>
+      <c r="F255" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G255" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H255" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I255" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J255" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K255" s="1" t="inlineStr"/>
+      <c r="L255" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="M255" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N255" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="O255" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P255" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>564751</v>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t>Backgrounder - Transfer and Discontinuance of Railway Lines</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/backgrounder-transfer-and-discontinuance-railway-lines</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/fiche-dinformation-transferts-et-cessation-dexploitation-lignes</t>
+        </is>
+      </c>
+      <c r="E256" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, January 7, 2016</t>
+        </is>
+      </c>
+      <c r="F256" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G256" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H256" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I256" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J256" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K256" s="1" t="inlineStr"/>
+      <c r="L256" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="M256" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="N256" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="O256" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P256" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>418500</v>
+      </c>
+      <c r="B257" s="1" t="inlineStr">
+        <is>
+          <t>The process for transferring or discontinuing railway line operations</t>
+        </is>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/process-transferring-or-discontinuing-railway-line-operations</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/processus-transfert-ou-cessation-dexploitation-dune-ligne-chemin-fer</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 28, 2014</t>
+        </is>
+      </c>
+      <c r="F257" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G257" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H257" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I257" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J257" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K257" s="1" t="inlineStr"/>
+      <c r="L257" s="1" t="n">
+        <v>353</v>
+      </c>
+      <c r="M257" s="1" t="n">
+        <v>556</v>
+      </c>
+      <c r="N257" s="1" t="n">
+        <v>566</v>
+      </c>
+      <c r="O257" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P257" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>418129</v>
+      </c>
+      <c r="B258" s="1" t="inlineStr">
+        <is>
+          <t>Railway line construction and relocation</t>
+        </is>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/railway-line-construction-and-relocation</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/construction-et-relocalisation-lignes</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t>Friday, October 4, 2019</t>
+        </is>
+      </c>
+      <c r="F258" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G258" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H258" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I258" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J258" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K258" s="1" t="inlineStr"/>
+      <c r="L258" s="1" t="n">
+        <v>484</v>
+      </c>
+      <c r="M258" s="1" t="n">
+        <v>647</v>
+      </c>
+      <c r="N258" s="1" t="n">
+        <v>631</v>
+      </c>
+      <c r="O258" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P258" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>92730</v>
+      </c>
+      <c r="B259" s="1" t="inlineStr">
+        <is>
+          <t>Air Carrier Licence Search</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-carrier-licence-search</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/recherche-licences-dun-transporteur-aerien</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, January 22, 2014</t>
+        </is>
+      </c>
+      <c r="F259" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G259" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H259" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I259" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J259" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K259" s="1" t="inlineStr"/>
+      <c r="L259" s="1" t="n">
+        <v>582</v>
+      </c>
+      <c r="M259" s="1" t="n">
+        <v>812</v>
+      </c>
+      <c r="N259" s="1" t="n">
+        <v>734</v>
+      </c>
+      <c r="O259" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P259" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>92909</v>
+      </c>
+      <c r="B260" s="1" t="inlineStr">
+        <is>
+          <t>Certificats d'aptitude (licences) pour les compagnies de chemin de fer de compétence fédérale</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="inlineStr"/>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/certificats-daptitude-licences-pour-compagnies-chemin-fer-competence-federale</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="inlineStr">
+        <is>
+          <t>Monday, November 28, 2022</t>
+        </is>
+      </c>
+      <c r="F260" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G260" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H260" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I260" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J260" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K260" s="1" t="inlineStr">
+        <is>
+          <t>Missing EN</t>
+        </is>
+      </c>
+      <c r="L260" s="1" t="inlineStr"/>
+      <c r="M260" s="1" t="inlineStr"/>
+      <c r="N260" s="1" t="inlineStr"/>
+      <c r="O260" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P260" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>568482</v>
+      </c>
+      <c r="B261" s="1" t="inlineStr">
+        <is>
+          <t>CTA releases What We Heard Report summarizing its rail transportation consultations</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/cta-releases-what-we-heard-report-summarizing-its-rail-transportation-consultations</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/lotc-publie-rapport-ce-que-nous-avons-entendu-resumant-ses-consultations-sur-transport</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t>Monday, March 4, 2019</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G261" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H261" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I261" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J261" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K261" s="1" t="inlineStr"/>
+      <c r="L261" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="M261" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="N261" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O261" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P261" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>97498</v>
+      </c>
+      <c r="B262" s="1" t="inlineStr">
+        <is>
+          <t>Effective December 28th, 2019 - Notification to Air Carriers of Upward Revision of the Limits of Liability Governed by the Montreal Convention</t>
+        </is>
+      </c>
+      <c r="C262" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/notification-air-carriers-upward-revision-limits-liability-international-transportation-</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/avis-aux-transporteurs-aeriens-concernant-la-revision-la-hausse-des-limites-de-responsab</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, November 16, 2016</t>
+        </is>
+      </c>
+      <c r="F262" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G262" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H262" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I262" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J262" s="1" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="K262" s="1" t="inlineStr">
+        <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
+      <c r="L262" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="M262" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="N262" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="O262" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P262" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>570070</v>
+      </c>
+      <c r="B263" s="1" t="inlineStr">
+        <is>
+          <t>New minimum liability insurance coverage requirement effective July 1, 2021</t>
+        </is>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/new-minimum-liability-insurance-coverage-requirement-effective-july-1-2021</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nouvelle-exigence-couverture-dassurance-responsabilite-minimale-vigueur-1er-juillet-2021</t>
+        </is>
+      </c>
+      <c r="E263" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, June 3, 2021</t>
+        </is>
+      </c>
+      <c r="F263" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G263" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H263" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I263" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J263" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K263" s="1" t="inlineStr"/>
+      <c r="L263" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="M263" s="1" t="n">
+        <v>598</v>
+      </c>
+      <c r="N263" s="1" t="n">
+        <v>594</v>
+      </c>
+      <c r="O263" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P263" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>570062</v>
+      </c>
+      <c r="B264" s="1" t="inlineStr">
+        <is>
+          <t>The Canadian Transportation Agency (CTA) service standards and performance information for fiscal year 2020 to 2021</t>
+        </is>
+      </c>
+      <c r="C264" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/canadian-transportation-agency-cta-service-standards-and-performance-information-fiscal-year-2020</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/normes-service-et-rendement-loffice-des-transports-canada-otc-pour-lexercice-2020-2021</t>
+        </is>
+      </c>
+      <c r="E264" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, May 27, 2021</t>
+        </is>
+      </c>
+      <c r="F264" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G264" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H264" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I264" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J264" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K264" s="1" t="inlineStr"/>
+      <c r="L264" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M264" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N264" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O264" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P264" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>570043</v>
+      </c>
+      <c r="B265" s="1" t="inlineStr">
+        <is>
+          <t>Railway noise and vibration</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/railway-noise-and-vibration</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/bruit-et-vibrations-ferroviaires</t>
+        </is>
+      </c>
+      <c r="E265" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 19, 2021</t>
+        </is>
+      </c>
+      <c r="F265" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G265" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H265" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I265" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J265" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K265" s="1" t="inlineStr"/>
+      <c r="L265" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="M265" s="1" t="n">
+        <v>309</v>
+      </c>
+      <c r="N265" s="1" t="n">
+        <v>298</v>
+      </c>
+      <c r="O265" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P265" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>568397</v>
+      </c>
+      <c r="B266" s="1" t="inlineStr">
+        <is>
+          <t>2019 Vancouver Freight Rail Investigation</t>
+        </is>
+      </c>
+      <c r="C266" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/2019-vancouver-freight-rail-investigation</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/2019-enquete-transport-ferroviaire-marchandises-vancouver</t>
+        </is>
+      </c>
+      <c r="E266" s="1" t="inlineStr">
+        <is>
+          <t>Friday, January 11, 2019</t>
+        </is>
+      </c>
+      <c r="F266" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G266" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H266" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I266" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J266" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K266" s="1" t="inlineStr"/>
+      <c r="L266" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="M266" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="N266" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="O266" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P266" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>563183</v>
+      </c>
+      <c r="B267" s="1" t="inlineStr">
+        <is>
+          <t>Code Share and Wet Lease Authorities</t>
+        </is>
+      </c>
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/code-share-and-wet-lease-authorities</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/autorites-de-partage-de-codes-et-de-reservation-de-capacite-et-dentente-de-location-daeronefs</t>
+        </is>
+      </c>
+      <c r="E267" s="1" t="inlineStr">
+        <is>
+          <t>Monday, May 15, 2017</t>
+        </is>
+      </c>
+      <c r="F267" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G267" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H267" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I267" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J267" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K267" s="1" t="inlineStr"/>
+      <c r="L267" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M267" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N267" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O267" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P267" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>566826</v>
+      </c>
+      <c r="B268" s="1" t="inlineStr">
+        <is>
+          <t>Principles related to level of service arbitration objections</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/principles-related-level-service-arbitration-objections</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/principes-lies-aux-oppositions-deposees-dans-cadre-larbitrage-ferroviaire-portant-sur-niveau</t>
+        </is>
+      </c>
+      <c r="E268" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, October 21, 2015</t>
+        </is>
+      </c>
+      <c r="F268" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G268" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H268" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I268" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J268" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K268" s="1" t="inlineStr"/>
+      <c r="L268" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M268" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N268" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O268" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P268" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>418498</v>
+      </c>
+      <c r="B269" s="1" t="inlineStr">
+        <is>
+          <t>Agreements: apportionment of costs of grade separations</t>
+        </is>
+      </c>
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/agreements-apportionment-costs-grade-separations</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ententes-sur-repartition-des-couts-des-sauts-mouton</t>
+        </is>
+      </c>
+      <c r="E269" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, June 25, 2015</t>
+        </is>
+      </c>
+      <c r="F269" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G269" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H269" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I269" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J269" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K269" s="1" t="inlineStr"/>
+      <c r="L269" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="M269" s="1" t="n">
+        <v>324</v>
+      </c>
+      <c r="N269" s="1" t="n">
+        <v>332</v>
+      </c>
+      <c r="O269" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P269" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>418497</v>
+      </c>
+      <c r="B270" s="1" t="inlineStr">
+        <is>
+          <t>Agreements: road and utility crossings</t>
+        </is>
+      </c>
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/agreements-road-and-utility-crossings</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ententes-sur-franchissements-routiers-et-par-desserte</t>
+        </is>
+      </c>
+      <c r="E270" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, June 25, 2015</t>
+        </is>
+      </c>
+      <c r="F270" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G270" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H270" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I270" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J270" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K270" s="1" t="inlineStr"/>
+      <c r="L270" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="M270" s="1" t="n">
+        <v>359</v>
+      </c>
+      <c r="N270" s="1" t="n">
+        <v>351</v>
+      </c>
+      <c r="O270" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P270" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>418313</v>
+      </c>
+      <c r="B271" s="1" t="inlineStr">
+        <is>
+          <t>Agreements: railway crossings of other railways</t>
+        </is>
+      </c>
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/agreements-railway-crossings-other-railways</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ententes-sur-croisements-dautres-lignes-chemin-fer</t>
+        </is>
+      </c>
+      <c r="E271" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, March 30, 2016</t>
+        </is>
+      </c>
+      <c r="F271" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G271" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H271" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I271" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J271" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K271" s="1" t="inlineStr"/>
+      <c r="L271" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="M271" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="N271" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="O271" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P271" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>418124</v>
+      </c>
+      <c r="B272" s="1" t="inlineStr">
+        <is>
+          <t>Supporting air tariff documents</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/supporting-air-tariff-documents</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/documents-dappui-pour-tarifs-aeriens</t>
+        </is>
+      </c>
+      <c r="E272" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, April 2, 2015</t>
+        </is>
+      </c>
+      <c r="F272" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G272" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H272" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I272" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J272" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K272" s="1" t="inlineStr"/>
+      <c r="L272" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="M272" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="N272" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="O272" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P272" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>93883</v>
+      </c>
+      <c r="B273" s="1" t="inlineStr">
+        <is>
+          <t>Railway Noise Measurement and Reporting Methodology - Detailed Descriptions</t>
+        </is>
+      </c>
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/railway-noise-measurement-and-reporting-methodology-detailed-descriptions</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/resume-methodologie-mesure-et-presentation-dun-rapport-sur-bruit-ferroviaire-descriptions-detaillees</t>
+        </is>
+      </c>
+      <c r="E273" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, December 5, 2013</t>
+        </is>
+      </c>
+      <c r="F273" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G273" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H273" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I273" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J273" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K273" s="1" t="inlineStr"/>
+      <c r="L273" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="M273" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="N273" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="O273" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P273" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>569741</v>
+      </c>
+      <c r="B274" s="1" t="inlineStr">
+        <is>
+          <t>FAQs: Drone Operations and Air Cargo Licencing</t>
+        </is>
+      </c>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/faqs-drone-operations-and-air-cargo-licencing</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faq-licences-pour-lutilisation-drones-et-transport-aerien-marchandises</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, December 3, 2020</t>
+        </is>
+      </c>
+      <c r="F274" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G274" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H274" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I274" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J274" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K274" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L274" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="M274" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="N274" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="O274" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P274" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>418696</v>
+      </c>
+      <c r="B275" s="1" t="inlineStr">
+        <is>
+          <t>Service Standards - Charter Permits for Canadian Originating Non-Scheduled International Air Services</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/service-standards-charter-permits-canadian-originating-non-scheduled-international-air-services</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/permis-daffretement-services-aeriens-internationaux-a-demande-provenance-canada</t>
+        </is>
+      </c>
+      <c r="E275" s="1" t="inlineStr">
+        <is>
+          <t>Monday, December 5, 2016</t>
+        </is>
+      </c>
+      <c r="F275" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G275" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H275" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I275" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J275" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K275" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L275" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M275" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N275" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O275" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P275" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>418937</v>
+      </c>
+      <c r="B276" s="1" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/rwanda</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/rwanda</t>
+        </is>
+      </c>
+      <c r="E276" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 21, 2014</t>
+        </is>
+      </c>
+      <c r="F276" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G276" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H276" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I276" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J276" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K276" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L276" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M276" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="N276" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O276" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P276" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>418933</v>
+      </c>
+      <c r="B277" s="1" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/honduras</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/honduras</t>
+        </is>
+      </c>
+      <c r="E277" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 21, 2014</t>
+        </is>
+      </c>
+      <c r="F277" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G277" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H277" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I277" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J277" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K277" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L277" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M277" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N277" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="O277" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P277" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>418929</v>
+      </c>
+      <c r="B278" s="1" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="C278" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/curacao</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/curacao</t>
+        </is>
+      </c>
+      <c r="E278" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 21, 2014</t>
+        </is>
+      </c>
+      <c r="F278" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G278" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H278" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I278" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J278" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K278" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L278" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M278" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N278" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O278" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P278" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>418927</v>
+      </c>
+      <c r="B279" s="1" t="inlineStr">
+        <is>
+          <t>Sint Maarten</t>
+        </is>
+      </c>
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/sint-maarten</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/sint-maarten</t>
+        </is>
+      </c>
+      <c r="E279" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 21, 2014</t>
+        </is>
+      </c>
+      <c r="F279" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G279" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H279" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I279" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J279" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K279" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L279" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M279" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="N279" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O279" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P279" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>418925</v>
+      </c>
+      <c r="B280" s="1" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C280" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/qatar</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/qatar</t>
+        </is>
+      </c>
+      <c r="E280" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 21, 2014</t>
+        </is>
+      </c>
+      <c r="F280" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G280" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H280" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I280" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J280" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K280" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L280" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="M280" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="N280" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="O280" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P280" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>418922</v>
+      </c>
+      <c r="B281" s="1" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C281" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/colombia</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/colombie</t>
+        </is>
+      </c>
+      <c r="E281" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 21, 2014</t>
+        </is>
+      </c>
+      <c r="F281" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G281" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H281" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I281" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J281" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K281" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L281" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="M281" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="N281" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="O281" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P281" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>93991</v>
+      </c>
+      <c r="B282" s="1" t="inlineStr">
+        <is>
+          <t>Netherlands Antilles</t>
+        </is>
+      </c>
+      <c r="C282" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/netherlands-antilles</t>
+        </is>
+      </c>
+      <c r="D282" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/antilles-neerlandaises</t>
+        </is>
+      </c>
+      <c r="E282" s="1" t="inlineStr">
+        <is>
+          <t>Monday, April 26, 2010</t>
+        </is>
+      </c>
+      <c r="F282" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G282" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H282" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I282" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J282" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K282" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L282" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M282" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N282" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O282" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P282" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>93946</v>
+      </c>
+      <c r="B283" s="1" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/ethiopia</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/ethiopie</t>
+        </is>
+      </c>
+      <c r="E283" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, April 22, 2010</t>
+        </is>
+      </c>
+      <c r="F283" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G283" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H283" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I283" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J283" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K283" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L283" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M283" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N283" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="O283" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P283" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>94021</v>
+      </c>
+      <c r="B284" s="1" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C284" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/tunisia</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/tunisie</t>
+        </is>
+      </c>
+      <c r="E284" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, April 22, 2010</t>
+        </is>
+      </c>
+      <c r="F284" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G284" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H284" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I284" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J284" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K284" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L284" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="M284" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="N284" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="O284" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P284" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>94023</v>
+      </c>
+      <c r="B285" s="1" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="C285" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/turkey</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/turquie</t>
+        </is>
+      </c>
+      <c r="E285" s="1" t="inlineStr">
+        <is>
+          <t>Friday, July 31, 2009</t>
+        </is>
+      </c>
+      <c r="F285" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G285" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H285" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I285" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J285" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K285" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L285" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="M285" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="N285" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="O285" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P285" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>93996</v>
+      </c>
+      <c r="B286" s="1" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C286" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/panama</t>
+        </is>
+      </c>
+      <c r="D286" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/panama</t>
+        </is>
+      </c>
+      <c r="E286" s="1" t="inlineStr">
+        <is>
+          <t>Sunday, February 1, 2009</t>
+        </is>
+      </c>
+      <c r="F286" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G286" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H286" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I286" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J286" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K286" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L286" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M286" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="N286" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O286" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P286" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>93923</v>
+      </c>
+      <c r="B287" s="1" t="inlineStr">
+        <is>
+          <t>Barbados</t>
+        </is>
+      </c>
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/barbados</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/barbade</t>
+        </is>
+      </c>
+      <c r="E287" s="1" t="inlineStr">
+        <is>
+          <t>Friday, February 8, 2008</t>
+        </is>
+      </c>
+      <c r="F287" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G287" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H287" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I287" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J287" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K287" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L287" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M287" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N287" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O287" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P287" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>94003</v>
+      </c>
+      <c r="B288" s="1" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C288" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/singapore</t>
+        </is>
+      </c>
+      <c r="D288" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/singapour</t>
+        </is>
+      </c>
+      <c r="E288" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, November 1, 2007</t>
+        </is>
+      </c>
+      <c r="F288" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G288" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H288" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I288" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J288" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K288" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L288" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="M288" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="N288" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="O288" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P288" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>93935</v>
+      </c>
+      <c r="B289" s="1" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C289" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/croatia</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/croatie</t>
+        </is>
+      </c>
+      <c r="E289" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, October 10, 2007</t>
+        </is>
+      </c>
+      <c r="F289" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G289" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H289" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I289" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J289" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K289" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L289" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M289" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N289" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O289" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P289" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>94001</v>
+      </c>
+      <c r="B290" s="1" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="C290" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/serbia</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/serbie</t>
+        </is>
+      </c>
+      <c r="E290" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, October 10, 2007</t>
+        </is>
+      </c>
+      <c r="F290" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G290" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H290" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I290" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J290" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K290" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L290" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="M290" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="N290" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="O290" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P290" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>94062</v>
+      </c>
+      <c r="B291" s="1" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="C291" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/iceland</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/islande</t>
+        </is>
+      </c>
+      <c r="E291" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, July 11, 2007</t>
+        </is>
+      </c>
+      <c r="F291" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G291" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H291" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I291" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J291" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K291" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L291" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="M291" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N291" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="O291" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P291" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>93966</v>
+      </c>
+      <c r="B292" s="1" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C292" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/jordan</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/jordanie</t>
+        </is>
+      </c>
+      <c r="E292" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 6, 2007</t>
+        </is>
+      </c>
+      <c r="F292" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G292" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H292" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I292" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J292" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K292" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L292" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M292" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N292" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O292" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P292" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>93973</v>
+      </c>
+      <c r="B293" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="C293" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/kuwait</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/koweit</t>
+        </is>
+      </c>
+      <c r="E293" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, May 8, 2007</t>
+        </is>
+      </c>
+      <c r="F293" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G293" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H293" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I293" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J293" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K293" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L293" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="M293" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N293" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O293" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P293" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>93951</v>
+      </c>
+      <c r="B294" s="1" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="C294" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/guyana</t>
+        </is>
+      </c>
+      <c r="D294" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/guyana</t>
+        </is>
+      </c>
+      <c r="E294" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, January 23, 2007</t>
+        </is>
+      </c>
+      <c r="F294" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G294" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H294" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I294" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J294" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K294" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L294" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M294" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N294" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O294" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P294" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>93941</v>
+      </c>
+      <c r="B295" s="1" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C295" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/egypt</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/egypte</t>
+        </is>
+      </c>
+      <c r="E295" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 5, 2006</t>
+        </is>
+      </c>
+      <c r="F295" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G295" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H295" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I295" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J295" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K295" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L295" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M295" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N295" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="O295" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P295" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>93908</v>
+      </c>
+      <c r="B296" s="1" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C296" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/algeria</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/algerie</t>
+        </is>
+      </c>
+      <c r="E296" s="1" t="inlineStr"/>
+      <c r="F296" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G296" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H296" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I296" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J296" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K296" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L296" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="M296" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="N296" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="O296" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P296" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>93912</v>
+      </c>
+      <c r="B297" s="1" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C297" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/aruba</t>
+        </is>
+      </c>
+      <c r="D297" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/aruba</t>
+        </is>
+      </c>
+      <c r="E297" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, August 2, 2006</t>
+        </is>
+      </c>
+      <c r="F297" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G297" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H297" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I297" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J297" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K297" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L297" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M297" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N297" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O297" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P297" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>94055</v>
+      </c>
+      <c r="B298" s="1" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="C298" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/peru</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/perou</t>
+        </is>
+      </c>
+      <c r="E298" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, April 14, 2005</t>
+        </is>
+      </c>
+      <c r="F298" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G298" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H298" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I298" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J298" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K298" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L298" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="M298" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="N298" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="O298" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P298" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>93933</v>
+      </c>
+      <c r="B299" s="1" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/china</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/chine</t>
+        </is>
+      </c>
+      <c r="E299" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, April 6, 2005</t>
+        </is>
+      </c>
+      <c r="F299" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G299" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H299" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I299" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J299" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K299" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L299" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="M299" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="N299" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="O299" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P299" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>94033</v>
+      </c>
+      <c r="B300" s="1" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C300" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/vietnam</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/vietnam</t>
+        </is>
+      </c>
+      <c r="E300" s="1" t="inlineStr">
+        <is>
+          <t>Friday, December 3, 2004</t>
+        </is>
+      </c>
+      <c r="F300" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G300" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H300" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I300" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J300" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K300" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L300" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="M300" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="N300" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="O300" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P300" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>93969</v>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/ivory-coast</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/cote-divoire</t>
+        </is>
+      </c>
+      <c r="E301" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, October 30, 2002</t>
+        </is>
+      </c>
+      <c r="F301" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G301" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H301" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I301" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J301" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K301" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L301" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="M301" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N301" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="O301" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P301" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>94025</v>
+      </c>
+      <c r="B302" s="1" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/ukraine</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/ukraine</t>
+        </is>
+      </c>
+      <c r="E302" s="1" t="inlineStr">
+        <is>
+          <t>Monday, February 25, 2002</t>
+        </is>
+      </c>
+      <c r="F302" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G302" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H302" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I302" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J302" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K302" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L302" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M302" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N302" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O302" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P302" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>93932</v>
+      </c>
+      <c r="B303" s="1" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="C303" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/chile</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/chili</t>
+        </is>
+      </c>
+      <c r="E303" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, August 16, 2001</t>
+        </is>
+      </c>
+      <c r="F303" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G303" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H303" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I303" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J303" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K303" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L303" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="M303" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="N303" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="O303" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P303" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>93980</v>
+      </c>
+      <c r="B304" s="1" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="C304" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/morocco</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/maroc</t>
+        </is>
+      </c>
+      <c r="E304" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, February 21, 2001</t>
+        </is>
+      </c>
+      <c r="F304" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G304" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H304" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I304" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J304" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K304" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L304" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M304" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N304" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="O304" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P304" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>93983</v>
+      </c>
+      <c r="B305" s="1" t="inlineStr">
+        <is>
+          <t>Nicaragua</t>
+        </is>
+      </c>
+      <c r="C305" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/nicaragua</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/nicaragua</t>
+        </is>
+      </c>
+      <c r="E305" s="1" t="inlineStr">
+        <is>
+          <t>Friday, January 5, 2001</t>
+        </is>
+      </c>
+      <c r="F305" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G305" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H305" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I305" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J305" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K305" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L305" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M305" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N305" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O305" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P305" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>94066</v>
+      </c>
+      <c r="B306" s="1" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="C306" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/guatemala</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/guatemala</t>
+        </is>
+      </c>
+      <c r="E306" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, December 27, 2000</t>
+        </is>
+      </c>
+      <c r="F306" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G306" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H306" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I306" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J306" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K306" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L306" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="M306" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="N306" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="O306" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P306" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>94048</v>
+      </c>
+      <c r="B307" s="1" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/dominican-republic</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/republique-dominicaine</t>
+        </is>
+      </c>
+      <c r="E307" s="1" t="inlineStr">
+        <is>
+          <t>Friday, December 22, 2000</t>
+        </is>
+      </c>
+      <c r="F307" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G307" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H307" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I307" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J307" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K307" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L307" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M307" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N307" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O307" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P307" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>93944</v>
+      </c>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/el-salvador</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/el-salvador</t>
+        </is>
+      </c>
+      <c r="E308" s="1" t="inlineStr">
+        <is>
+          <t>Sunday, September 17, 2000</t>
+        </is>
+      </c>
+      <c r="F308" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G308" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H308" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I308" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J308" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K308" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L308" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M308" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N308" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="O308" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P308" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>94031</v>
+      </c>
+      <c r="B309" s="1" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/venezuela</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/venezuela</t>
+        </is>
+      </c>
+      <c r="E309" s="1" t="inlineStr">
+        <is>
+          <t>Monday, November 23, 1998</t>
+        </is>
+      </c>
+      <c r="F309" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G309" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H309" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I309" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J309" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K309" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L309" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M309" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N309" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O309" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P309" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>93985</v>
+      </c>
+      <c r="B310" s="1" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/norway</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/norvege</t>
+        </is>
+      </c>
+      <c r="E310" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, June 24, 1997</t>
+        </is>
+      </c>
+      <c r="F310" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G310" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H310" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I310" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J310" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K310" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L310" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M310" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N310" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="O310" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P310" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>93953</v>
+      </c>
+      <c r="B311" s="1" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C311" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/indonesia</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/indonesie</t>
+        </is>
+      </c>
+      <c r="E311" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 5, 1995</t>
+        </is>
+      </c>
+      <c r="F311" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G311" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H311" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I311" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J311" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K311" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L311" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M311" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="N311" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="O311" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P311" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>94019</v>
+      </c>
+      <c r="B312" s="1" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="C312" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/trinidad-and-tobago</t>
+        </is>
+      </c>
+      <c r="D312" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/trinite-et-tobago</t>
+        </is>
+      </c>
+      <c r="E312" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, January 26, 1995</t>
+        </is>
+      </c>
+      <c r="F312" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G312" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H312" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I312" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J312" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K312" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L312" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M312" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N312" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O312" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P312" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
+        <v>93967</v>
+      </c>
+      <c r="B313" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C313" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/india</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/inde</t>
+        </is>
+      </c>
+      <c r="E313" s="1" t="inlineStr">
+        <is>
+          <t>Monday, June 20, 1994</t>
+        </is>
+      </c>
+      <c r="F313" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G313" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H313" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I313" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J313" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K313" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L313" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="M313" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="N313" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="O313" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P313" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>93963</v>
+      </c>
+      <c r="B314" s="1" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C314" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/japan</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/japon</t>
+        </is>
+      </c>
+      <c r="E314" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, June 2, 1994</t>
+        </is>
+      </c>
+      <c r="F314" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G314" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H314" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I314" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J314" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K314" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L314" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="M314" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="N314" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="O314" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P314" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>93987</v>
+      </c>
+      <c r="B315" s="1" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/pakistan</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/pakistan</t>
+        </is>
+      </c>
+      <c r="E315" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, April 7, 1994</t>
+        </is>
+      </c>
+      <c r="F315" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G315" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H315" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I315" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J315" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K315" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L315" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="M315" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="N315" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="O315" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P315" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>93910</v>
+      </c>
+      <c r="B316" s="1" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C316" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/argentina</t>
+        </is>
+      </c>
+      <c r="D316" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/argentine</t>
+        </is>
+      </c>
+      <c r="E316" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, December 9, 1993</t>
+        </is>
+      </c>
+      <c r="F316" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G316" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H316" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I316" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J316" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K316" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L316" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="M316" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="N316" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="O316" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P316" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>93999</v>
+      </c>
+      <c r="B317" s="1" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C317" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/saudi-arabia</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/arabie-saoudite</t>
+        </is>
+      </c>
+      <c r="E317" s="1" t="inlineStr">
+        <is>
+          <t>Sunday, June 9, 1991</t>
+        </is>
+      </c>
+      <c r="F317" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G317" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H317" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I317" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J317" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K317" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L317" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="M317" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="N317" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="O317" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P317" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>94014</v>
+      </c>
+      <c r="B318" s="1" t="inlineStr">
+        <is>
+          <t>St. Christopher (St. Kitts) and Nevis</t>
+        </is>
+      </c>
+      <c r="C318" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/st-christopher-st-kitts-and-nevis</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/st-christophe-st-kitts-et-nevis</t>
+        </is>
+      </c>
+      <c r="E318" s="1" t="inlineStr">
+        <is>
+          <t>Friday, October 18, 1985</t>
+        </is>
+      </c>
+      <c r="F318" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G318" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H318" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I318" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J318" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K318" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L318" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M318" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N318" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O318" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P318" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>94017</v>
+      </c>
+      <c r="B319" s="1" t="inlineStr">
+        <is>
+          <t>Saint Lucia</t>
+        </is>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/saint-lucia</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/sainte-lucie</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, March 8, 1984</t>
+        </is>
+      </c>
+      <c r="F319" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G319" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H319" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I319" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J319" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K319" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L319" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M319" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N319" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O319" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P319" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>93993</v>
+      </c>
+      <c r="B320" s="1" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C320" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreement/haiti</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entente-matiere-transport/haiti</t>
+        </is>
+      </c>
+      <c r="E320" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, October 12, 1978</t>
+        </is>
+      </c>
+      <c r="F320" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G320" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H320" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I320" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J320" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K320" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L320" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M320" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N320" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O320" s="1" t="inlineStr">
+        <is>
+          <t>Air Agreements</t>
+        </is>
+      </c>
+      <c r="P320" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>563422</v>
+      </c>
+      <c r="B321" s="1" t="inlineStr">
+        <is>
+          <t>New filing approach for international scheduled services air cargo tariffs</t>
+        </is>
+      </c>
+      <c r="C321" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/new-filing-approach-international-scheduled-services-air-cargo-tariffs</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/nouvelle-methode-depot-tarifs-relatifs-au-transport-international-regulier-marchandises</t>
+        </is>
+      </c>
+      <c r="E321" s="1" t="inlineStr">
+        <is>
+          <t>Monday, October 5, 2015</t>
+        </is>
+      </c>
+      <c r="F321" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G321" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H321" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I321" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J321" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K321" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L321" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M321" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N321" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="O321" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P321" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>97158</v>
+      </c>
+      <c r="B322" s="1" t="inlineStr">
+        <is>
+          <t>Operation of season-long charter programs by U.S. air carriers on behalf of all professional sports teams</t>
+        </is>
+      </c>
+      <c r="C322" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/operation-season-long-charter-programs-us-air-carriers-behalf-all-professional-sports</t>
+        </is>
+      </c>
+      <c r="D322" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/execution-programmes-vols-affretes-pour-une-saison-complete-par-des-transporteurs</t>
+        </is>
+      </c>
+      <c r="E322" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, September 26, 2019</t>
+        </is>
+      </c>
+      <c r="F322" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G322" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H322" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I322" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J322" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K322" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L322" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="M322" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="N322" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="O322" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P322" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="n">
+        <v>567607</v>
+      </c>
+      <c r="B323" s="1" t="inlineStr">
+        <is>
+          <t>Chair and CEO Scott Streiner addresses the Standing Committee on Transportation and Communications, Senate of Canada on January 30, 2018</t>
+        </is>
+      </c>
+      <c r="C323" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/chair-and-ceo-scott-streiner-addresses-standing-committee-transportation-and-communications-senate-of-canada-january-30-2018</t>
+        </is>
+      </c>
+      <c r="D323" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/president-et-premier-dirigeant-scott-streiner-sadressant-a-comite-des-transports-et-des-communications-du-senat-du-canada-30-janvier-2018</t>
+        </is>
+      </c>
+      <c r="E323" s="1" t="inlineStr">
+        <is>
+          <t>Monday, January 29, 2018</t>
+        </is>
+      </c>
+      <c r="F323" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G323" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H323" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I323" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J323" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K323" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L323" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M323" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="N323" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O323" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P323" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="n">
+        <v>567303</v>
+      </c>
+      <c r="B324" s="1" t="inlineStr">
+        <is>
+          <t>Chair and CEO Scott Streiner addresses the Standing Committee on Transport, Infrastructure and Communities on September 11, 2017</t>
+        </is>
+      </c>
+      <c r="C324" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/chair-and-ceo-scott-streiner-addresses-standing-committee-transport-infrastructure-and</t>
+        </is>
+      </c>
+      <c r="D324" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/president-et-premier-dirigeant-scott-streiner-sadressant-au-comite-permanent-des-transports</t>
+        </is>
+      </c>
+      <c r="E324" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, September 12, 2017</t>
+        </is>
+      </c>
+      <c r="F324" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G324" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H324" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I324" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J324" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K324" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L324" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M324" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N324" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O324" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P324" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="n">
+        <v>567082</v>
+      </c>
+      <c r="B325" s="1" t="inlineStr">
+        <is>
+          <t>Chair and CEO Scott Streiner addresses the International Association of Airport Executives Canada on June 7, 2017</t>
+        </is>
+      </c>
+      <c r="C325" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/chair-and-ceo-scott-streiner-addresses-international-association-airport-executives-canada</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/president-et-premier-dirigeant-scott-streiner-sadressant-a-international-association-airport</t>
+        </is>
+      </c>
+      <c r="E325" s="1" t="inlineStr">
+        <is>
+          <t>Friday, June 9, 2017</t>
+        </is>
+      </c>
+      <c r="F325" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G325" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H325" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I325" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J325" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K325" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L325" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="M325" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="N325" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O325" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P325" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="n">
+        <v>566931</v>
+      </c>
+      <c r="B326" s="1" t="inlineStr">
+        <is>
+          <t>Chair and CEO Scott Streiner addresses the RBC Canadian Automotive and Industrials Conference on May 18, 2017</t>
+        </is>
+      </c>
+      <c r="C326" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/chair-and-ceo-scott-streiner-addresses-rbc-canadian-automotive-and-industrials-conference</t>
+        </is>
+      </c>
+      <c r="D326" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/president-et-premier-dirigeant-scott-streiner-prend-parole-a-loccasion-rbc-canadian</t>
+        </is>
+      </c>
+      <c r="E326" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, May 18, 2017</t>
+        </is>
+      </c>
+      <c r="F326" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G326" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H326" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I326" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J326" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K326" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L326" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M326" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="N326" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="O326" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P326" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>568851</v>
+      </c>
+      <c r="B327" s="1" t="inlineStr">
+        <is>
+          <t>Long-Haul Interswitching (LHI) - How to Provide an Undertaking to the Local Carrier</t>
+        </is>
+      </c>
+      <c r="C327" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/lhi-how-provide-undertaking-local-carrier</t>
+        </is>
+      </c>
+      <c r="D327" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ild-comment-presenter-engagement-transporteur-local</t>
+        </is>
+      </c>
+      <c r="E327" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 15, 2019</t>
+        </is>
+      </c>
+      <c r="F327" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G327" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H327" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I327" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J327" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K327" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L327" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M327" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N327" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="O327" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P327" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="n">
+        <v>568850</v>
+      </c>
+      <c r="B328" s="1" t="inlineStr">
+        <is>
+          <t>Long-Haul Interswitching (LHI) - How to Authorize Someone Who is Not a Lawyer to Represent Your Company</t>
+        </is>
+      </c>
+      <c r="C328" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/long-haul-interswitching-lhi-how-authorize-someone-who-not-a-lawyer-represent-your-company</t>
+        </is>
+      </c>
+      <c r="D328" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ild-comment-autoriser-personne</t>
+        </is>
+      </c>
+      <c r="E328" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 15, 2019</t>
+        </is>
+      </c>
+      <c r="F328" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G328" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H328" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I328" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J328" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K328" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L328" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M328" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N328" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O328" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P328" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="n">
+        <v>568849</v>
+      </c>
+      <c r="B329" s="1" t="inlineStr">
+        <is>
+          <t>Long-Haul Interswitching (LHI) - How to Request Confidentiality</t>
+        </is>
+      </c>
+      <c r="C329" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/long-haul-interswitching-lhi-how-request-confidentiality</t>
+        </is>
+      </c>
+      <c r="D329" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ild-comment-presenter-requete-confidentialite</t>
+        </is>
+      </c>
+      <c r="E329" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 15, 2019</t>
+        </is>
+      </c>
+      <c r="F329" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G329" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H329" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I329" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J329" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K329" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L329" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M329" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N329" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O329" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P329" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="n">
+        <v>568591</v>
+      </c>
+      <c r="B330" s="1" t="inlineStr">
+        <is>
+          <t>Service standard: Air Service Licences Issued</t>
+        </is>
+      </c>
+      <c r="C330" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/service-standard-air-service-licences-issued</t>
+        </is>
+      </c>
+      <c r="D330" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/norme-service-licences-dexploitation-services-aeriens-delivrees</t>
+        </is>
+      </c>
+      <c r="E330" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, May 2, 2019</t>
+        </is>
+      </c>
+      <c r="F330" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G330" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H330" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I330" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J330" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K330" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L330" s="1" t="inlineStr"/>
+      <c r="M330" s="1" t="inlineStr"/>
+      <c r="N330" s="1" t="inlineStr"/>
+      <c r="O330" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P330" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="n">
+        <v>568434</v>
+      </c>
+      <c r="B331" s="1" t="inlineStr">
+        <is>
+          <t>Vancouver Freight Rail Investigation - Additional information from the public</t>
+        </is>
+      </c>
+      <c r="C331" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/vancouver-freight-rail-investigation-additional-information-public</t>
+        </is>
+      </c>
+      <c r="D331" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/enquete-sur-transport-ferroviaire-marchandises-a-vancouver-information-supplementaire-public</t>
+        </is>
+      </c>
+      <c r="E331" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, February 5, 2019</t>
+        </is>
+      </c>
+      <c r="F331" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G331" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H331" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I331" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J331" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K331" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L331" s="1" t="inlineStr"/>
+      <c r="M331" s="1" t="inlineStr"/>
+      <c r="N331" s="1" t="inlineStr"/>
+      <c r="O331" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P331" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="n">
+        <v>568432</v>
+      </c>
+      <c r="B332" s="1" t="inlineStr">
+        <is>
+          <t>Opening remarks: Oral hearing on possible rail service issues in Vancouver</t>
+        </is>
+      </c>
+      <c r="C332" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/opening-remarks-oral-hearing-possible-rail-service-issues-vancouver</t>
+        </is>
+      </c>
+      <c r="D332" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/mot-douverture-audience-sur-problemes-possibles-lies-au-service-transport-ferroviaire-a-vancouver</t>
+        </is>
+      </c>
+      <c r="E332" s="1" t="inlineStr">
+        <is>
+          <t>Monday, February 4, 2019</t>
+        </is>
+      </c>
+      <c r="F332" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G332" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H332" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I332" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J332" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K332" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L332" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M332" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N332" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O332" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P332" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="n">
+        <v>568413</v>
+      </c>
+      <c r="B333" s="1" t="inlineStr">
+        <is>
+          <t>Order of Proceedings for Vancouver Freight Rail Investigation Oral Hearing</t>
+        </is>
+      </c>
+      <c r="C333" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/order-proceedings-vancouver-freight-rail-investigation-oral-hearing</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ordre-deliberations-vancouver-audience-enquete-transport-ferroviaire-marchandises</t>
+        </is>
+      </c>
+      <c r="E333" s="1" t="inlineStr">
+        <is>
+          <t>Friday, January 25, 2019</t>
+        </is>
+      </c>
+      <c r="F333" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G333" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H333" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I333" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J333" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K333" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L333" s="1" t="inlineStr"/>
+      <c r="M333" s="1" t="inlineStr"/>
+      <c r="N333" s="1" t="inlineStr"/>
+      <c r="O333" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P333" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="n">
+        <v>281691</v>
+      </c>
+      <c r="B334" s="1" t="inlineStr">
+        <is>
+          <t>Standard for Air Service Licences 2017-2018</t>
+        </is>
+      </c>
+      <c r="C334" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/standard-air-service-licences-2017-2018</t>
+        </is>
+      </c>
+      <c r="D334" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/norme-service-pour-licences-dexploitation-services-aeriens-2017-2018</t>
+        </is>
+      </c>
+      <c r="E334" s="1" t="inlineStr">
+        <is>
+          <t>Monday, May 15, 2017</t>
+        </is>
+      </c>
+      <c r="F334" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G334" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H334" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I334" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J334" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K334" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L334" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M334" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N334" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O334" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P334" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="n">
+        <v>418692</v>
+      </c>
+      <c r="B335" s="1" t="inlineStr">
+        <is>
+          <t>Charter Permits for Canadian Originating Non-Scheduled International Air Services 2017-2018</t>
+        </is>
+      </c>
+      <c r="C335" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/charter-permits-canadian-originating-non-scheduled-international-air-services-2017-2018</t>
+        </is>
+      </c>
+      <c r="D335" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/permis-daffretement-pour-services-aeriens-internationaux-a-demande-provenance-canada-2017-2018</t>
+        </is>
+      </c>
+      <c r="E335" s="1" t="inlineStr">
+        <is>
+          <t>Monday, May 15, 2017</t>
+        </is>
+      </c>
+      <c r="F335" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G335" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H335" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I335" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J335" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K335" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L335" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="M335" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N335" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="O335" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P335" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="n">
+        <v>562266</v>
+      </c>
+      <c r="B336" s="1" t="inlineStr">
+        <is>
+          <t>Interpretation Policy</t>
+        </is>
+      </c>
+      <c r="C336" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/interpretation-policy</t>
+        </is>
+      </c>
+      <c r="D336" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/politique-dinterpretation</t>
+        </is>
+      </c>
+      <c r="E336" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, March 30, 2017</t>
+        </is>
+      </c>
+      <c r="F336" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G336" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H336" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I336" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J336" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K336" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L336" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M336" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N336" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O336" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P336" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="n">
+        <v>566813</v>
+      </c>
+      <c r="B337" s="1" t="inlineStr">
+        <is>
+          <t>How to apply for level of service arbitration</t>
+        </is>
+      </c>
+      <c r="C337" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/how-apply-level-service-arbitration</t>
+        </is>
+      </c>
+      <c r="D337" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/comment-presenter-une-demande-darbitrage-portant-sur-niveau-service</t>
+        </is>
+      </c>
+      <c r="E337" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, June 21, 2016</t>
+        </is>
+      </c>
+      <c r="F337" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G337" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H337" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I337" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J337" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K337" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L337" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M337" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N337" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O337" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P337" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>418809</v>
+      </c>
+      <c r="B338" s="1" t="inlineStr">
+        <is>
+          <t>Interline Baggage Rules for Canada</t>
+        </is>
+      </c>
+      <c r="C338" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/interline-baggage-rules-canada</t>
+        </is>
+      </c>
+      <c r="D338" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/regles-canada-concernant-bagages-pour-voyages-intercompagnies</t>
+        </is>
+      </c>
+      <c r="E338" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, April 1, 2015</t>
+        </is>
+      </c>
+      <c r="F338" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G338" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H338" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I338" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J338" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K338" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L338" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M338" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N338" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O338" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P338" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="n">
+        <v>418499</v>
+      </c>
+      <c r="B339" s="1" t="inlineStr">
+        <is>
+          <t>How to relocate railway lines in urban areas</t>
+        </is>
+      </c>
+      <c r="C339" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/how-relocate-railway-lines-urban-areas</t>
+        </is>
+      </c>
+      <c r="D339" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/comment-deplacer-des-lignes-chemin-fer-zones-urbaines</t>
+        </is>
+      </c>
+      <c r="E339" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, June 21, 2016</t>
+        </is>
+      </c>
+      <c r="F339" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G339" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H339" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I339" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J339" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K339" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L339" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="M339" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="N339" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="O339" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P339" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="n">
+        <v>418184</v>
+      </c>
+      <c r="B340" s="1" t="inlineStr">
+        <is>
+          <t>Filing a service schedule with the Agency</t>
+        </is>
+      </c>
+      <c r="C340" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/filing-a-service-schedule-agency</t>
+        </is>
+      </c>
+      <c r="D340" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/depot-dun-indicateur-aupres-loffice</t>
+        </is>
+      </c>
+      <c r="E340" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, May 6, 2014</t>
+        </is>
+      </c>
+      <c r="F340" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G340" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H340" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I340" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J340" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K340" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L340" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="M340" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="N340" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="O340" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P340" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="n">
+        <v>100002</v>
+      </c>
+      <c r="B341" s="1" t="inlineStr">
+        <is>
+          <t>Working at the Agency</t>
+        </is>
+      </c>
+      <c r="C341" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/working-at-agency</t>
+        </is>
+      </c>
+      <c r="D341" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/travailler-a-loffice</t>
+        </is>
+      </c>
+      <c r="E341" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 4, 2016</t>
+        </is>
+      </c>
+      <c r="F341" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G341" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H341" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I341" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J341" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K341" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L341" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="M341" s="1" t="n">
+        <v>344</v>
+      </c>
+      <c r="N341" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="O341" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P341" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="n">
+        <v>93802</v>
+      </c>
+      <c r="B342" s="1" t="inlineStr">
+        <is>
+          <t>Transport agreements</t>
+        </is>
+      </c>
+      <c r="C342" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transport-agreements</t>
+        </is>
+      </c>
+      <c r="D342" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/ententes-matiere-transport-aerien</t>
+        </is>
+      </c>
+      <c r="E342" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, September 21, 2016</t>
+        </is>
+      </c>
+      <c r="F342" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G342" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H342" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I342" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J342" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K342" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L342" s="1" t="n">
+        <v>808</v>
+      </c>
+      <c r="M342" s="1" t="n">
+        <v>1385</v>
+      </c>
+      <c r="N342" s="1" t="n">
+        <v>1231</v>
+      </c>
+      <c r="O342" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P342" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="n">
+        <v>418207</v>
+      </c>
+      <c r="B343" s="1" t="inlineStr">
+        <is>
+          <t>Instructions on filling out the non-Canadian air licence application form</t>
+        </is>
+      </c>
+      <c r="C343" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/instructions-filling-out-non-canadian-air-licence-application-form</t>
+        </is>
+      </c>
+      <c r="D343" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/instructions-pour-remplir-formulaire-demande-licence-dair-non-canadien</t>
+        </is>
+      </c>
+      <c r="E343" s="1" t="inlineStr">
+        <is>
+          <t>Monday, February 24, 2014</t>
+        </is>
+      </c>
+      <c r="F343" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="G343" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H343" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I343" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J343" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K343" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L343" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="M343" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="N343" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="O343" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P343" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n">
+        <v>97339</v>
+      </c>
+      <c r="B344" s="1" t="inlineStr">
+        <is>
+          <t>Certificate of Insurance (APPENDIX I)</t>
+        </is>
+      </c>
+      <c r="C344" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/certificate-insurance-appendix-i</t>
+        </is>
+      </c>
+      <c r="D344" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/certificat-dassurance-annexe-i</t>
+        </is>
+      </c>
+      <c r="E344" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, March 7, 2017</t>
+        </is>
+      </c>
+      <c r="F344" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G344" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H344" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I344" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J344" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K344" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L344" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M344" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N344" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O344" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P344" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="n">
+        <v>96875</v>
+      </c>
+      <c r="B345" s="1" t="inlineStr">
+        <is>
+          <t>Filing Advice for Tariff - Schedule IV (Section 114)</t>
+        </is>
+      </c>
+      <c r="C345" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/filing-advice-tariff-schedule-iv-section-114</t>
+        </is>
+      </c>
+      <c r="D345" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/avis-depot-tarif-annexe-iv-article-114</t>
+        </is>
+      </c>
+      <c r="E345" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, September 30, 2015</t>
+        </is>
+      </c>
+      <c r="F345" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G345" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H345" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I345" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J345" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K345" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L345" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M345" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N345" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O345" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P345" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="n">
+        <v>566143</v>
+      </c>
+      <c r="B346" s="1" t="inlineStr">
+        <is>
+          <t>Chair and CEO Scott Streiner addresses the Chartered Institute of Logistics and Transport in North America (CILTNA) on November 14, 2016</t>
+        </is>
+      </c>
+      <c r="C346" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/chair-and-ceo-scott-streiner-addresses-chartered-institute-logistics-and-transport-north</t>
+        </is>
+      </c>
+      <c r="D346" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/le-president-et-premier-dirigeant-scott-streiner-sadressant-a-linstitut-agree-de-la</t>
+        </is>
+      </c>
+      <c r="E346" s="1" t="inlineStr">
+        <is>
+          <t>Friday, November 18, 2016</t>
+        </is>
+      </c>
+      <c r="F346" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G346" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H346" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I346" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J346" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K346" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L346" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M346" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N346" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O346" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P346" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="n">
+        <v>566393</v>
+      </c>
+      <c r="B347" s="1" t="inlineStr">
+        <is>
+          <t>Chair and CEO Scott Streiner addresses the Pulse and Special Crops Convention on July 7, 2016</t>
+        </is>
+      </c>
+      <c r="C347" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/chair-and-ceo-scott-streiner-addresses-pulse-and-special-crops-convention-july-7-2016</t>
+        </is>
+      </c>
+      <c r="D347" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/le-president-et-premier-dirigeant-scott-streiner-sadressant-aux-participants-du-congres-de-lAssociation-canadienne-des-cultures-speciales-le7-juillet-2016</t>
+        </is>
+      </c>
+      <c r="E347" s="1" t="inlineStr">
+        <is>
+          <t>Monday, July 11, 2016</t>
+        </is>
+      </c>
+      <c r="F347" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G347" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H347" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I347" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J347" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K347" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L347" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M347" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="N347" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O347" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P347" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="n">
+        <v>567279</v>
+      </c>
+      <c r="B348" s="1" t="inlineStr">
+        <is>
+          <t>Chairman's Opening Remarks - Air Transat Hearing</t>
+        </is>
+      </c>
+      <c r="C348" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/chairmans-opening-remarks-air-transat-hearing</t>
+        </is>
+      </c>
+      <c r="D348" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/mot-douverture-president-audience-air-transat</t>
+        </is>
+      </c>
+      <c r="E348" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, August 30, 2017</t>
+        </is>
+      </c>
+      <c r="F348" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G348" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H348" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I348" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J348" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K348" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L348" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M348" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="N348" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O348" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P348" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="n">
+        <v>93519</v>
+      </c>
+      <c r="B349" s="1" t="inlineStr">
+        <is>
+          <t>Sample signage on the availability of tariffs</t>
+        </is>
+      </c>
+      <c r="C349" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/sample-signage-availability-tariffs</t>
+        </is>
+      </c>
+      <c r="D349" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/modeles-panneaux-daffichage-sur-disponibilite-des-tarifs</t>
+        </is>
+      </c>
+      <c r="E349" s="1" t="inlineStr"/>
+      <c r="F349" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G349" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H349" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I349" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J349" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K349" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L349" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="M349" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="N349" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="O349" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P349" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="n">
+        <v>566847</v>
+      </c>
+      <c r="B350" s="1" t="inlineStr">
+        <is>
+          <t>Additional information required for applications about crossings</t>
+        </is>
+      </c>
+      <c r="C350" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/additional-information-required-applications-about-crossings</t>
+        </is>
+      </c>
+      <c r="D350" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/node/566847</t>
+        </is>
+      </c>
+      <c r="E350" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 20, 2015</t>
+        </is>
+      </c>
+      <c r="F350" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G350" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H350" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I350" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J350" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K350" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L350" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M350" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N350" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O350" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P350" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="n">
+        <v>562762</v>
+      </c>
+      <c r="B351" s="1" t="inlineStr">
+        <is>
+          <t>FAQs: Railway Traffic Liability Regulations</t>
+        </is>
+      </c>
+      <c r="C351" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/faqs-railway-traffic-liability-regulations</t>
+        </is>
+      </c>
+      <c r="D351" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faq-reglement-sur-responsabilite-a-legard-transport-ferroviaire-des-marchandises</t>
+        </is>
+      </c>
+      <c r="E351" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 23, 2014</t>
+        </is>
+      </c>
+      <c r="F351" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G351" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H351" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I351" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J351" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K351" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L351" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="M351" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="N351" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="O351" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P351" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="n">
+        <v>562760</v>
+      </c>
+      <c r="B352" s="1" t="inlineStr">
+        <is>
+          <t>FAQs: Railway Traffic and Passenger Tariffs Regulations</t>
+        </is>
+      </c>
+      <c r="C352" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/faqs-railway-traffic-and-passenger-tariffs-regulations</t>
+        </is>
+      </c>
+      <c r="D352" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faq-reglement-sur-tarifs-transport-ferroviaire-des-marchandises-et-des-passagers</t>
+        </is>
+      </c>
+      <c r="E352" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 23, 2014</t>
+        </is>
+      </c>
+      <c r="F352" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G352" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H352" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I352" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J352" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K352" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L352" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M352" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N352" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O352" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P352" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="n">
+        <v>562750</v>
+      </c>
+      <c r="B353" s="1" t="inlineStr">
+        <is>
+          <t>FAQs: Regulations on Operational Terms for Rail Level of Services Arbitration</t>
+        </is>
+      </c>
+      <c r="C353" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/faqs-regulations-operational-terms-rail-level-services-arbitration</t>
+        </is>
+      </c>
+      <c r="D353" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faq-reglement-sur-conditions-dexploitation-visees-par-larbitrage-ferroviaire-portant-sur-niveau</t>
+        </is>
+      </c>
+      <c r="E353" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 23, 2014</t>
+        </is>
+      </c>
+      <c r="F353" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G353" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H353" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I353" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J353" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K353" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L353" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M353" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N353" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O353" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P353" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="n">
+        <v>418808</v>
+      </c>
+      <c r="B354" s="1" t="inlineStr">
+        <is>
+          <t>Interline baggage rules for Canada: questions and answers</t>
+        </is>
+      </c>
+      <c r="C354" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/interline-baggage-rules-canada-questions-and-answers</t>
+        </is>
+      </c>
+      <c r="D354" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/regles-canada-concernant-bagages-pour-voyages-intercompagnies-questions-et-reponses</t>
+        </is>
+      </c>
+      <c r="E354" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, August 26, 2014</t>
+        </is>
+      </c>
+      <c r="F354" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G354" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H354" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I354" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J354" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K354" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L354" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="M354" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="N354" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="O354" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P354" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="n">
+        <v>418131</v>
+      </c>
+      <c r="B355" s="1" t="inlineStr">
+        <is>
+          <t>Depreciation rates</t>
+        </is>
+      </c>
+      <c r="C355" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/depreciation-rates</t>
+        </is>
+      </c>
+      <c r="D355" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/taux-damortissement</t>
+        </is>
+      </c>
+      <c r="E355" s="1" t="inlineStr">
+        <is>
+          <t>Monday, April 7, 2014</t>
+        </is>
+      </c>
+      <c r="F355" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G355" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H355" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I355" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J355" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K355" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L355" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="M355" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="N355" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="O355" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P355" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="n">
+        <v>93645</v>
+      </c>
+      <c r="B356" s="1" t="inlineStr">
+        <is>
+          <t>Decision No. 149-R-2012 - Additional Information</t>
+        </is>
+      </c>
+      <c r="C356" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/decision-no-149-r-2012-additional-information</t>
+        </is>
+      </c>
+      <c r="D356" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/decision-149-r-2012-informations-supplementaires</t>
+        </is>
+      </c>
+      <c r="E356" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, December 5, 2013</t>
+        </is>
+      </c>
+      <c r="F356" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G356" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H356" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I356" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J356" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K356" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L356" s="1" t="inlineStr"/>
+      <c r="M356" s="1" t="inlineStr"/>
+      <c r="N356" s="1" t="inlineStr"/>
+      <c r="O356" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P356" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="n">
+        <v>92815</v>
+      </c>
+      <c r="B357" s="1" t="inlineStr">
+        <is>
+          <t>Decision on Process for Cost of Capital Methodology Review</t>
+        </is>
+      </c>
+      <c r="C357" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/decision-process-cost-capital-methodology-review</t>
+        </is>
+      </c>
+      <c r="D357" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/decision-portant-sur-processus-dexamen-methode-detablissement-cout-capital</t>
+        </is>
+      </c>
+      <c r="E357" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, November 26, 2013</t>
+        </is>
+      </c>
+      <c r="F357" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G357" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H357" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I357" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J357" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K357" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L357" s="1" t="inlineStr"/>
+      <c r="M357" s="1" t="inlineStr"/>
+      <c r="N357" s="1" t="inlineStr"/>
+      <c r="O357" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P357" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="n">
+        <v>92283</v>
+      </c>
+      <c r="B358" s="1" t="inlineStr">
+        <is>
+          <t>Stakeholder Comment: James Nolan</t>
+        </is>
+      </c>
+      <c r="C358" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/stakeholder-comment-james-nolan</t>
+        </is>
+      </c>
+      <c r="D358" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/commentaire-des-intervenants-james-nolan</t>
+        </is>
+      </c>
+      <c r="E358" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, March 26, 2015</t>
+        </is>
+      </c>
+      <c r="F358" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G358" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H358" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I358" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J358" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K358" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L358" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M358" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N358" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O358" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P358" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="n">
+        <v>93097</v>
+      </c>
+      <c r="B359" s="1" t="inlineStr">
+        <is>
+          <t>Cost of Capital Methodology Review - Correspondence from the Agency Secretary – January 18, 2010</t>
+        </is>
+      </c>
+      <c r="C359" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/cost-capital-methodology-review-correspondence-agency-secretary-january-18-2010</t>
+        </is>
+      </c>
+      <c r="D359" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/examen-methode-detablissement-cout-capital-des-compagnies-chemin-fer-correspondance-secretaire</t>
+        </is>
+      </c>
+      <c r="E359" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, November 26, 2013</t>
+        </is>
+      </c>
+      <c r="F359" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G359" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H359" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I359" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J359" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K359" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L359" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="M359" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="N359" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O359" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P359" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="n">
+        <v>92750</v>
+      </c>
+      <c r="B360" s="1" t="inlineStr">
+        <is>
+          <t>Extension of Deadline for Consultation Submissions</t>
+        </is>
+      </c>
+      <c r="C360" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/extension-deadline-consultation-submissions</t>
+        </is>
+      </c>
+      <c r="D360" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/prolongation-delai-pour-presentation-commentaires</t>
+        </is>
+      </c>
+      <c r="E360" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, November 26, 2013</t>
+        </is>
+      </c>
+      <c r="F360" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G360" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H360" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I360" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J360" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K360" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L360" s="1" t="inlineStr"/>
+      <c r="M360" s="1" t="inlineStr"/>
+      <c r="N360" s="1" t="inlineStr"/>
+      <c r="O360" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P360" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="n">
+        <v>92296</v>
+      </c>
+      <c r="B361" s="1" t="inlineStr">
+        <is>
+          <t>Letter to Stakeholders: Invitation to Participate in Consultations</t>
+        </is>
+      </c>
+      <c r="C361" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/letter-stakeholders-invitation-participate-consultations</t>
+        </is>
+      </c>
+      <c r="D361" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/lettre-a-lintention-des-intervenants-invitation-a-participer-aux-consultations</t>
+        </is>
+      </c>
+      <c r="E361" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, November 26, 2013</t>
+        </is>
+      </c>
+      <c r="F361" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G361" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H361" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I361" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J361" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K361" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L361" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M361" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N361" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O361" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P361" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="n">
+        <v>93103</v>
+      </c>
+      <c r="B362" s="1" t="inlineStr">
+        <is>
+          <t>Decision No. LET-R-26-2008 - Review of the Railway Interswitching Regulations</t>
+        </is>
+      </c>
+      <c r="C362" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/decision-no-let-r-26-2008-review-railway-interswitching-regulations</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/decision-no-let-r-26-2008-revision-reglement-sur-linterconnexion-trafic-ferroviaire</t>
+        </is>
+      </c>
+      <c r="E362" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, November 18, 2014</t>
+        </is>
+      </c>
+      <c r="F362" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G362" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H362" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I362" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J362" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K362" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L362" s="1" t="inlineStr"/>
+      <c r="M362" s="1" t="inlineStr"/>
+      <c r="N362" s="1" t="inlineStr"/>
+      <c r="O362" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P362" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="n">
+        <v>92746</v>
+      </c>
+      <c r="B363" s="1" t="inlineStr">
+        <is>
+          <t>Advisory: One-time Adjustment to Grain Revenue Cap Inflation Index</t>
+        </is>
+      </c>
+      <c r="C363" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/advisory-one-time-adjustment-grain-revenue-cap-inflation-index</t>
+        </is>
+      </c>
+      <c r="D363" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/avis-ajustement-ponctuel-au-taux-dinflation-pour-plafonds-revenu-grain</t>
+        </is>
+      </c>
+      <c r="E363" s="1" t="inlineStr">
+        <is>
+          <t>Friday, November 13, 2015</t>
+        </is>
+      </c>
+      <c r="F363" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G363" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H363" s="1" t="inlineStr">
+        <is>
+          <t>National Transportation System</t>
+        </is>
+      </c>
+      <c r="I363" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J363" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K363" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L363" s="1" t="inlineStr"/>
+      <c r="M363" s="1" t="inlineStr"/>
+      <c r="N363" s="1" t="inlineStr"/>
+      <c r="O363" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P363" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
